--- a/examples/月末客户对账/跟进清单.xlsx
+++ b/examples/月末客户对账/跟进清单.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>0.7.0</t>
+          <t>0.8.0</t>
         </is>
       </c>
     </row>
